--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/DELAWARE_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/DELAWARE_2019.xlsx
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C261">
